--- a/data/trans_dic/P19E_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Clase-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,42; 29,58</t>
+          <t>20,7; 29,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 19,72</t>
+          <t>13,4; 20,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 18,2</t>
+          <t>10,35; 17,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,22</t>
+          <t>6,56; 11,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,9; 23,17</t>
+          <t>16,85; 23,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 14,89</t>
+          <t>10,66; 14,8</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,53; 28,47</t>
+          <t>20,0; 28,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 25,81</t>
+          <t>17,51; 25,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 20,5</t>
+          <t>12,69; 20,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 14,23</t>
+          <t>8,73; 13,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 23,19</t>
+          <t>17,02; 23,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,39; 19,54</t>
+          <t>14,36; 19,55</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,9; 39,25</t>
+          <t>31,03; 39,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 30,43</t>
+          <t>7,12; 30,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,58; 26,39</t>
+          <t>14,0; 27,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 19,49</t>
+          <t>11,22; 19,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,63; 34,75</t>
+          <t>27,48; 34,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 25,99</t>
+          <t>7,73; 26,42</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,5; 42,33</t>
+          <t>36,49; 42,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,31; 34,8</t>
+          <t>28,35; 34,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,72; 22,5</t>
+          <t>16,84; 22,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 14,31</t>
+          <t>5,36; 14,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,05; 33,2</t>
+          <t>28,89; 33,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,29; 24,3</t>
+          <t>14,37; 24,7</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,54; 47,79</t>
+          <t>39,81; 48,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,28; 40,69</t>
+          <t>31,34; 40,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,98; 33,93</t>
+          <t>26,4; 33,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,66; 25,82</t>
+          <t>16,51; 25,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,96; 39,12</t>
+          <t>33,5; 39,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,32; 29,95</t>
+          <t>22,03; 29,86</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,57; 30,95</t>
+          <t>19,97; 30,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,02; 14,15</t>
+          <t>3,72; 14,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,83; 32,78</t>
+          <t>27,06; 33,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,71; 23,73</t>
+          <t>18,63; 23,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,17; 31,55</t>
+          <t>26,58; 31,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,74; 20,13</t>
+          <t>15,63; 20,17</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,14; 36,35</t>
+          <t>33,13; 36,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,73; 26,56</t>
+          <t>18,82; 26,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,41; 25,27</t>
+          <t>22,55; 25,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,73; 17,0</t>
+          <t>12,39; 17,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,19; 30,41</t>
+          <t>28,2; 30,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,3</t>
+          <t>17,28; 21,34</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86333; 125080</t>
+          <t>87528; 125570</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64917; 99499</t>
+          <t>67587; 103331</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36186; 62635</t>
+          <t>35603; 60427</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28725; 50143</t>
+          <t>29297; 51628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>129614; 177720</t>
+          <t>129201; 177014</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>103279; 141662</t>
+          <t>101397; 140764</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71516; 104216</t>
+          <t>73212; 105783</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79461; 116574</t>
+          <t>79082; 116034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46114; 75501</t>
+          <t>46742; 77239</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33580; 54363</t>
+          <t>33355; 52965</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125435; 170266</t>
+          <t>125011; 169522</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>120010; 162895</t>
+          <t>119742; 162969</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>157451; 199996</t>
+          <t>158124; 201640</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43624; 202352</t>
+          <t>47335; 200526</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22144; 43030</t>
+          <t>22818; 44311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18946; 32382</t>
+          <t>18642; 32872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>185805; 233690</t>
+          <t>184795; 234185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60179; 215990</t>
+          <t>64250; 219618</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>405773; 470647</t>
+          <t>405692; 470479</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>290880; 357516</t>
+          <t>291263; 359237</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134857; 181498</t>
+          <t>135870; 183976</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51571; 139887</t>
+          <t>52407; 137460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>557324; 636916</t>
+          <t>554253; 638484</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>306434; 487106</t>
+          <t>287988; 495103</t>
         </is>
       </c>
     </row>
@@ -1816,32 +1816,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>236531; 285899</t>
+          <t>238128; 288654</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>147854; 192320</t>
+          <t>148126; 190876</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195193; 245479</t>
+          <t>191056; 242960</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139227; 215712</t>
+          <t>137949; 216358</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>448927; 517111</t>
+          <t>442850; 517680</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>291951; 391835</t>
+          <t>288208; 390637</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>54970; 86939</t>
+          <t>56101; 85062</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9666; 34037</t>
+          <t>8942; 34094</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>278835; 340643</t>
+          <t>281241; 345719</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>140196; 177846</t>
+          <t>139649; 175573</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>345461; 416529</t>
+          <t>350937; 415844</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>155812; 199287</t>
+          <t>154772; 199659</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1090006; 1195782</t>
+          <t>1089759; 1209281</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>629580; 892709</t>
+          <t>632780; 893452</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>771938; 870675</t>
+          <t>776795; 877696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>452983; 604821</t>
+          <t>440759; 610058</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1898255; 2048089</t>
+          <t>1899335; 2043516</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1184234; 1473628</t>
+          <t>1195329; 1476618</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19E_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,7; 29,7</t>
+          <t>20,72; 29,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 20,48</t>
+          <t>13,47; 20,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,35; 17,56</t>
+          <t>10,43; 17,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,55</t>
+          <t>6,4; 11,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,85; 23,08</t>
+          <t>17,03; 22,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 14,8</t>
+          <t>10,66; 14,88</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,0; 28,89</t>
+          <t>19,69; 28,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,51; 25,69</t>
+          <t>16,98; 24,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 20,97</t>
+          <t>12,04; 20,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,73; 13,86</t>
+          <t>8,36; 13,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 23,08</t>
+          <t>17,19; 23,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,36; 19,55</t>
+          <t>13,81; 18,61</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,03; 39,57</t>
+          <t>31,48; 39,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 30,16</t>
+          <t>23,73; 32,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,0; 27,18</t>
+          <t>13,3; 27,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,22; 19,78</t>
+          <t>10,38; 18,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,48; 34,82</t>
+          <t>27,72; 34,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 26,42</t>
+          <t>20,77; 26,91</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,49; 42,32</t>
+          <t>36,3; 42,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,35; 34,96</t>
+          <t>26,95; 32,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,81</t>
+          <t>17,04; 22,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 14,07</t>
+          <t>12,03; 15,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,89; 33,28</t>
+          <t>29,07; 33,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 24,7</t>
+          <t>21,39; 24,93</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,81; 48,26</t>
+          <t>39,94; 48,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,34; 40,39</t>
+          <t>30,74; 39,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,4; 33,58</t>
+          <t>26,82; 33,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,51; 25,89</t>
+          <t>21,89; 26,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,5; 39,17</t>
+          <t>33,93; 39,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,03; 29,86</t>
+          <t>26,45; 30,83</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,97; 30,28</t>
+          <t>20,07; 30,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,72; 14,18</t>
+          <t>4,34; 14,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,06; 33,26</t>
+          <t>27,18; 32,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,63; 23,43</t>
+          <t>18,69; 23,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,58; 31,5</t>
+          <t>26,37; 31,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,63; 20,17</t>
+          <t>16,08; 20,44</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,13; 36,76</t>
+          <t>33,1; 36,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,82; 26,58</t>
+          <t>23,9; 27,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,55; 25,48</t>
+          <t>22,45; 25,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,15</t>
+          <t>15,87; 18,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,2; 30,35</t>
+          <t>28,05; 30,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,28; 21,34</t>
+          <t>20,04; 21,91</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81964</t>
+          <t>89515</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>119901</t>
+          <t>130829</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87528; 125570</t>
+          <t>87614; 125616</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>67587; 103331</t>
+          <t>74091; 110259</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35603; 60427</t>
+          <t>35908; 60538</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29297; 51628</t>
+          <t>31232; 55005</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>129201; 177014</t>
+          <t>130600; 175795</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>101397; 140764</t>
+          <t>110643; 154458</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97866</t>
+          <t>99183</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42302</t>
+          <t>45431</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>140167</t>
+          <t>144615</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73212; 105783</t>
+          <t>72079; 105321</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79082; 116034</t>
+          <t>81934; 120029</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46742; 77239</t>
+          <t>44353; 76614</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33355; 52965</t>
+          <t>35321; 57022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125011; 169522</t>
+          <t>126242; 170560</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>119742; 162969</t>
+          <t>125004; 168420</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>122355</t>
+          <t>129981</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>25653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>146909</t>
+          <t>155634</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>158124; 201640</t>
+          <t>160385; 201240</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47335; 200526</t>
+          <t>111114; 150939</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22818; 44311</t>
+          <t>21679; 44127</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18642; 32872</t>
+          <t>19329; 33720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>184795; 234185</t>
+          <t>186411; 234906</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64250; 219618</t>
+          <t>135925; 176135</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>323457</t>
+          <t>336064</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104724</t>
+          <t>120348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>428181</t>
+          <t>456412</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>405692; 470479</t>
+          <t>403600; 467418</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>291263; 359237</t>
+          <t>302639; 364531</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>135870; 183976</t>
+          <t>137437; 184133</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52407; 137460</t>
+          <t>103489; 137348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>554253; 638484</t>
+          <t>557678; 638896</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>287988; 495103</t>
+          <t>424196; 494362</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>167972</t>
+          <t>197030</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186671</t>
+          <t>200472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>354644</t>
+          <t>397501</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>238128; 288654</t>
+          <t>238939; 290081</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148126; 190876</t>
+          <t>173357; 220229</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191056; 242960</t>
+          <t>194086; 244989</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137949; 216358</t>
+          <t>180765; 222564</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>442850; 517680</t>
+          <t>448470; 518666</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>288208; 390637</t>
+          <t>367670; 428599</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156330</t>
+          <t>175587</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>175293</t>
+          <t>194703</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56101; 85062</t>
+          <t>56393; 86618</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8942; 34094</t>
+          <t>10296; 34231</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>281241; 345719</t>
+          <t>282455; 341968</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>139649; 175573</t>
+          <t>155302; 195929</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>350937; 415844</t>
+          <t>348128; 416737</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>154772; 199659</t>
+          <t>171749; 218381</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>812578</t>
+          <t>870889</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>552518</t>
+          <t>608806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1365095</t>
+          <t>1479695</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1089759; 1209281</t>
+          <t>1088839; 1195463</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>632780; 893452</t>
+          <t>818574; 927205</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>776795; 877696</t>
+          <t>773492; 877321</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>440759; 610058</t>
+          <t>573571; 650555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1899335; 2043516</t>
+          <t>1888815; 2045590</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1195329; 1476618</t>
+          <t>1410670; 1541834</t>
         </is>
       </c>
     </row>
